--- a/01_Thermal/B_results/single_annular_bemt_params.xlsx
+++ b/01_Thermal/B_results/single_annular_bemt_params.xlsx
@@ -508,34 +508,34 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1561543863406598</v>
+        <v>0.1516618013801307</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1031362858421505</v>
+        <v>0.1018435301693847</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>74.18996719677371</v>
+        <v>67.61919498334521</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07018419497319295</v>
+        <v>0.06797329609303578</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2917526020043204</v>
+        <v>0.2915344141975234</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1764097096672853</v>
+        <v>0.1788218862659403</v>
       </c>
       <c r="K2" t="n">
-        <v>7.562844380899158</v>
+        <v>7.167467894583679</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6323323785528056</v>
+        <v>0.4378798599304675</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3588787940714297</v>
+        <v>0.1828318586006233</v>
       </c>
     </row>
     <row r="3">
@@ -551,34 +551,34 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1011422336763471</v>
+        <v>0.1010388328379924</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03358055578861409</v>
+        <v>0.03357097921449655</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>17.63581154164477</v>
+        <v>17.18294822023364</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006353666609356753</v>
+        <v>0.006347931299815749</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3283417992707197</v>
+        <v>0.3282567714478075</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2330060120385242</v>
+        <v>0.2327016189146754</v>
       </c>
       <c r="K3" t="n">
-        <v>5.035931398606792</v>
+        <v>5.044057560107008</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4305940267669616</v>
+        <v>0.4317217430893363</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1067635398798949</v>
+        <v>0.1056775611348438</v>
       </c>
     </row>
     <row r="4">
@@ -594,34 +594,34 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2350828228925933</v>
+        <v>0.239895384337964</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08260545932549608</v>
+        <v>0.08343557894953178</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>67.10046618977947</v>
+        <v>50.20476279183458</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01686208813193348</v>
+        <v>0.01634237167907551</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5426121372965643</v>
+        <v>0.528408941608548</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1692633177736018</v>
+        <v>0.1802055269612738</v>
       </c>
       <c r="K4" t="n">
-        <v>3.957843084197418</v>
+        <v>4.039390806531354</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7366502757860423</v>
+        <v>-0.8473911398660394</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1438639732169592</v>
+        <v>-0.1529618801954292</v>
       </c>
     </row>
     <row r="5">
@@ -637,34 +637,34 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2033179638965603</v>
+        <v>0.202405248191582</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05766799136985046</v>
+        <v>0.05865849796217078</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>84.46525348088838</v>
+        <v>80.50674698165412</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006484215592357054</v>
+        <v>0.005593693037265187</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3393851795648914</v>
+        <v>0.3429992094071918</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3680130807013923</v>
+        <v>0.3939927639831015</v>
       </c>
       <c r="K5" t="n">
-        <v>3.012759287869629</v>
+        <v>2.920078743650731</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2698629212353399</v>
+        <v>-0.2203970179126757</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1595185829671823</v>
+        <v>-0.1439158222154585</v>
       </c>
     </row>
     <row r="6">
@@ -680,34 +680,34 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2064612498753302</v>
+        <v>0.2051680622414827</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05973967117411868</v>
+        <v>0.05964630103599714</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>50.42049970834246</v>
+        <v>52.11336790378326</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00438043766911429</v>
+        <v>0.004430057303956649</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3910470552836028</v>
+        <v>0.3881766277870562</v>
       </c>
       <c r="J6" t="n">
-        <v>0.408042446445009</v>
+        <v>0.4082008099295733</v>
       </c>
       <c r="K6" t="n">
-        <v>2.194044775698651</v>
+        <v>2.213081913015671</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3658739315741111</v>
+        <v>0.3410005346529067</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.109144596485223</v>
+        <v>-0.1075695030640413</v>
       </c>
     </row>
     <row r="7">
@@ -723,34 +723,34 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1651045529937034</v>
+        <v>0.1528687681423447</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05589956072798076</v>
+        <v>0.05063289643502274</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>32.65015945690054</v>
+        <v>22.53831844861432</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01071984123566321</v>
+        <v>0.004606990643228085</v>
       </c>
       <c r="I7" t="n">
-        <v>0.377205479035101</v>
+        <v>0.3910227901720171</v>
       </c>
       <c r="J7" t="n">
-        <v>0.408328320961941</v>
+        <v>0.4265254569193407</v>
       </c>
       <c r="K7" t="n">
-        <v>2.388379897223092</v>
+        <v>2.437730267959238</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5084427965414687</v>
+        <v>0.2743453966574473</v>
       </c>
       <c r="M7" t="n">
-        <v>0.42206193800884</v>
+        <v>0.3338404901313784</v>
       </c>
     </row>
     <row r="8">
@@ -766,34 +766,34 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1063328739789045</v>
+        <v>0.1027875208905903</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04464454303919087</v>
+        <v>0.04436696240609413</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>29.22128096582225</v>
+        <v>31.15586063461939</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003211349275981237</v>
+        <v>0.001903798514703507</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3608043099733593</v>
+        <v>0.373722262226627</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5088274049625656</v>
+        <v>0.5402344185950633</v>
       </c>
       <c r="K8" t="n">
-        <v>2.00409304473081</v>
+        <v>2.000392604066759</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1075029176249896</v>
+        <v>0.03234766252532419</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06252532851349524</v>
+        <v>-0.007849475958429207</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/single_annular_bemt_params.xlsx
+++ b/01_Thermal/B_results/single_annular_bemt_params.xlsx
@@ -508,34 +508,34 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1516618013801307</v>
+        <v>0.1547990767431428</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1018435301693847</v>
+        <v>0.104091801748043</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>67.61919498334521</v>
+        <v>68.52526076688001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06797329609303578</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2915344141975234</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1788218862659403</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="K2" t="n">
-        <v>7.167467894583679</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4378798599304675</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1828318586006233</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="3">
@@ -551,34 +551,34 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1010388328379924</v>
+        <v>0.1010357186645347</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03357097921449655</v>
+        <v>0.0335708550292327</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>17.18294822023364</v>
+        <v>17.18491837255394</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006347931299815749</v>
+        <v>0.006348137147049251</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3282567714478075</v>
+        <v>0.3282513574397667</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2327016189146754</v>
+        <v>0.232699146541859</v>
       </c>
       <c r="K3" t="n">
-        <v>5.044057560107008</v>
+        <v>5.044141537278102</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4317217430893363</v>
+        <v>0.4309401543520813</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1056775611348438</v>
+        <v>0.105477770702859</v>
       </c>
     </row>
     <row r="4">
@@ -594,34 +594,34 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.239895384337964</v>
+        <v>0.2398761312030526</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08343557894953178</v>
+        <v>0.08343204688558509</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>50.20476279183458</v>
+        <v>50.21214828559781</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01634237167907551</v>
+        <v>0.01634175159786094</v>
       </c>
       <c r="I4" t="n">
-        <v>0.528408941608548</v>
+        <v>0.5284157369309818</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1802055269612738</v>
+        <v>0.1802048076861808</v>
       </c>
       <c r="K4" t="n">
-        <v>4.039390806531354</v>
+        <v>4.039407840451303</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8473911398660394</v>
+        <v>-0.846946164097601</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1529618801954292</v>
+        <v>-0.1529457134055473</v>
       </c>
     </row>
     <row r="5">
@@ -637,34 +637,34 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>0.202405248191582</v>
+        <v>0.2024141015568248</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05865849796217078</v>
+        <v>0.05865562515388366</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>80.50674698165412</v>
+        <v>80.50743864595552</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005593693037265187</v>
+        <v>0.005594277754569317</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3429992094071918</v>
+        <v>0.3430307268134909</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3939927639831015</v>
+        <v>0.3939664744956399</v>
       </c>
       <c r="K5" t="n">
-        <v>2.920078743650731</v>
+        <v>2.919961669146067</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2203970179126757</v>
+        <v>-0.2200726092836718</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1439158222154585</v>
+        <v>-0.1436840800512284</v>
       </c>
     </row>
     <row r="6">
@@ -680,34 +680,34 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2051680622414827</v>
+        <v>0.2051578423521764</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05964630103599714</v>
+        <v>0.059643920993966</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>52.11336790378326</v>
+        <v>52.11464480505771</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004430057303956649</v>
+        <v>0.004429954967125478</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3881766277870562</v>
+        <v>0.3881660412327387</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4082008099295733</v>
+        <v>0.4082088329497971</v>
       </c>
       <c r="K6" t="n">
-        <v>2.213081913015671</v>
+        <v>2.213157177817227</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3410005346529067</v>
+        <v>0.3407503783739789</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1075695030640413</v>
+        <v>-0.107486480940414</v>
       </c>
     </row>
     <row r="7">
@@ -723,34 +723,34 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1528687681423447</v>
+        <v>0.1528600868958526</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05063289643502274</v>
+        <v>0.05063216568540051</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>22.53831844861432</v>
+        <v>22.54018235928258</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004606990643228085</v>
+        <v>0.00460176958254147</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3910227901720171</v>
+        <v>0.3910207270923858</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4265254569193407</v>
+        <v>0.426544246606803</v>
       </c>
       <c r="K7" t="n">
-        <v>2.437730267959238</v>
+        <v>2.437781428041422</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2743453966574473</v>
+        <v>0.2740142934148945</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3338404901313784</v>
+        <v>0.3334234283338369</v>
       </c>
     </row>
     <row r="8">
@@ -766,34 +766,34 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1027875208905903</v>
+        <v>0.1027875540578658</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04436696240609413</v>
+        <v>0.04436707303952814</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>31.15586063461939</v>
+        <v>31.15587171146068</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001903798514703507</v>
+        <v>0.001903788516085271</v>
       </c>
       <c r="I8" t="n">
-        <v>0.373722262226627</v>
+        <v>0.3737216643966301</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5402344185950633</v>
+        <v>0.5402349451484891</v>
       </c>
       <c r="K8" t="n">
-        <v>2.000392604066759</v>
+        <v>2.000393454873399</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03234766252532419</v>
+        <v>0.03233889895000946</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.007849475958429207</v>
+        <v>-0.007849594993027099</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/single_annular_bemt_params.xlsx
+++ b/01_Thermal/B_results/single_annular_bemt_params.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,16 @@
           <t>b1</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,34 +518,40 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1547990767431428</v>
+        <v>0.1506008278104879</v>
       </c>
       <c r="E2" t="n">
-        <v>0.104091801748043</v>
+        <v>0.1088735840142028</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>68.52526076688001</v>
+        <v>83.90327921988663</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06843130419263244</v>
+        <v>0.08321777323475649</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3234119355523905</v>
+        <v>0.3267531353996254</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1641512027920073</v>
+        <v>0.1592142315968851</v>
       </c>
       <c r="K2" t="n">
-        <v>6.086974999998803</v>
+        <v>6.086974999998553</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3417922806996451</v>
+        <v>0.4500784376668589</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1211473581035549</v>
+        <v>0.09415691330475341</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.314785875998468</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4633983334006478</v>
       </c>
     </row>
     <row r="3">
@@ -551,34 +567,40 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1010357186645347</v>
+        <v>0.08207311649531132</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0335708550292327</v>
+        <v>0.02907103876275917</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>17.18491837255394</v>
+        <v>19.28114506371901</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006348137147049251</v>
+        <v>0.008384341400370881</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3282513574397667</v>
+        <v>0.323667251378589</v>
       </c>
       <c r="J3" t="n">
-        <v>0.232699146541859</v>
+        <v>0.2339611978038382</v>
       </c>
       <c r="K3" t="n">
-        <v>5.044141537278102</v>
+        <v>5.088974421483914</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4309401543520813</v>
+        <v>0.4146021544798534</v>
       </c>
       <c r="M3" t="n">
-        <v>0.105477770702859</v>
+        <v>0.1362677716981878</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.1828054695406122</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.025702511217095</v>
       </c>
     </row>
     <row r="4">
@@ -594,34 +616,40 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2398761312030526</v>
+        <v>0.2541772488164116</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08343204688558509</v>
+        <v>0.08507944980826321</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>50.21214828559781</v>
+        <v>59.36539756503853</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01634175159786094</v>
+        <v>0.02138040549404825</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5284157369309818</v>
+        <v>0.5264766940001046</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1802048076861808</v>
+        <v>0.1843331687081108</v>
       </c>
       <c r="K4" t="n">
-        <v>4.039407840451303</v>
+        <v>3.961601196597131</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.846946164097601</v>
+        <v>-0.9992704576236295</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1529457134055473</v>
+        <v>-0.03070415440489609</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3693800548231223</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.2249655880633936</v>
       </c>
     </row>
     <row r="5">
@@ -637,34 +665,40 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2024141015568248</v>
+        <v>0.1732306057592117</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05865562515388366</v>
+        <v>0.05739009997456995</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>80.50743864595552</v>
+        <v>102.0388985471538</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005594277754569317</v>
+        <v>0.007256628191884316</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3430307268134909</v>
+        <v>0.3315298022030728</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3939664744956399</v>
+        <v>0.4157485777967798</v>
       </c>
       <c r="K5" t="n">
-        <v>2.919961669146067</v>
+        <v>2.881802560377761</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2200726092836718</v>
+        <v>-0.4048600846470232</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1436840800512284</v>
+        <v>-0.1820131239736304</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1941091433986639</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.7502505853439153</v>
       </c>
     </row>
     <row r="6">
@@ -680,34 +714,40 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2051578423521764</v>
+        <v>0.1539726483147757</v>
       </c>
       <c r="E6" t="n">
-        <v>0.059643920993966</v>
+        <v>0.05219988618364381</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>52.11464480505771</v>
+        <v>59.99260928344965</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004429954967125478</v>
+        <v>0.006413601258043545</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3881660412327387</v>
+        <v>0.4023144864005901</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4082088329497971</v>
+        <v>0.3931140170889311</v>
       </c>
       <c r="K6" t="n">
-        <v>2.213157177817227</v>
+        <v>2.153894214091423</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3407503783739789</v>
+        <v>0.2534982534432125</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.107486480940414</v>
+        <v>-0.3782667062170901</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3723630141147607</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.6831018026581483</v>
       </c>
     </row>
     <row r="7">
@@ -723,34 +763,40 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1528600868958526</v>
+        <v>0.1485806114128822</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05063216568540051</v>
+        <v>0.05245648712334585</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>22.54018235928258</v>
+        <v>26.31670551137697</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00460176958254147</v>
+        <v>0.007281559057604298</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3910207270923858</v>
+        <v>0.4008533778421772</v>
       </c>
       <c r="J7" t="n">
-        <v>0.426544246606803</v>
+        <v>0.421242793993894</v>
       </c>
       <c r="K7" t="n">
-        <v>2.437781428041422</v>
+        <v>2.426871659489694</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2740142934148945</v>
+        <v>0.2513600927753623</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3334234283338369</v>
+        <v>0.385322480702235</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2380991796724366</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.02238401476897605</v>
       </c>
     </row>
     <row r="8">
@@ -766,34 +812,40 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1027875540578658</v>
+        <v>0.09870526653052931</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04436707303952814</v>
+        <v>0.04273066177694543</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>31.15587171146068</v>
+        <v>35.65723462265144</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001903788516085271</v>
+        <v>0.002918597112675284</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3737216643966301</v>
+        <v>0.3882706649423203</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5402349451484891</v>
+        <v>0.5312832446391645</v>
       </c>
       <c r="K8" t="n">
-        <v>2.000393454873399</v>
+        <v>1.999286954720624</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03233889895000946</v>
+        <v>-0.01991117448202358</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.007849594993027099</v>
+        <v>-0.0373186709377998</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1343341731495304</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1603946198391386</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/single_annular_bemt_params.xlsx
+++ b/01_Thermal/B_results/single_annular_bemt_params.xlsx
@@ -518,40 +518,40 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1506008278104879</v>
+        <v>0.1519837219982988</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1088735840142028</v>
+        <v>0.08072495773128997</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>83.90327921988663</v>
+        <v>58.37280698641612</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08321777323475649</v>
+        <v>0.03272727100230934</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3267531353996254</v>
+        <v>0.3261941025205431</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1592142315968851</v>
+        <v>0.1640863154085699</v>
       </c>
       <c r="K2" t="n">
-        <v>6.086974999998553</v>
+        <v>6.086974999999974</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4500784376668589</v>
+        <v>0.5213973820164834</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09415691330475341</v>
+        <v>0.01833918594600815</v>
       </c>
       <c r="N2" t="n">
-        <v>0.314785875998468</v>
+        <v>0.3124349295186446</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4633983334006478</v>
+        <v>0.3065603555780633</v>
       </c>
     </row>
     <row r="3">
@@ -567,40 +567,40 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08207311649531132</v>
+        <v>0.08083064437533767</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02907103876275917</v>
+        <v>0.02931203101784444</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>19.28114506371901</v>
+        <v>8.287301471153558</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008384341400370881</v>
+        <v>0.009777166758466663</v>
       </c>
       <c r="I3" t="n">
-        <v>0.323667251378589</v>
+        <v>0.3249706626873308</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2339611978038382</v>
+        <v>0.2277459752437846</v>
       </c>
       <c r="K3" t="n">
-        <v>5.088974421483914</v>
+        <v>5.12770899538702</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4146021544798534</v>
+        <v>0.4230373828174782</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1362677716981878</v>
+        <v>0.1190264249918382</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1828054695406122</v>
+        <v>-0.1631656107868411</v>
       </c>
       <c r="O3" t="n">
-        <v>1.025702511217095</v>
+        <v>1.031015945819364</v>
       </c>
     </row>
     <row r="4">
@@ -616,40 +616,40 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2541772488164116</v>
+        <v>0.2366546642235309</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08507944980826321</v>
+        <v>0.08177615025948948</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>59.36539756503853</v>
+        <v>65.67955717082663</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02138040549404825</v>
+        <v>0.01699823061018332</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5264766940001046</v>
+        <v>0.5385440176638251</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1843331687081108</v>
+        <v>0.176078734875025</v>
       </c>
       <c r="K4" t="n">
-        <v>3.961601196597131</v>
+        <v>3.888210673990142</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9992704576236295</v>
+        <v>-0.9359672813149343</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03070415440489609</v>
+        <v>-0.07154178292117275</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3693800548231223</v>
+        <v>-0.1392030687295198</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2249655880633936</v>
+        <v>0.2188911534119586</v>
       </c>
     </row>
     <row r="5">
@@ -665,40 +665,40 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1732306057592117</v>
+        <v>0.1564951359840181</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05739009997456995</v>
+        <v>0.05663639106978347</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>102.0388985471538</v>
+        <v>39.43585295889206</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007256628191884316</v>
+        <v>0.01290537763945257</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3315298022030728</v>
+        <v>0.3868246307004896</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4157485777967798</v>
+        <v>0.3482175860986065</v>
       </c>
       <c r="K5" t="n">
-        <v>2.881802560377761</v>
+        <v>2.949561235470975</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4048600846470232</v>
+        <v>-0.3317360942396267</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1820131239736304</v>
+        <v>-0.2952988191539074</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1941091433986639</v>
+        <v>0.1991232011505641</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7502505853439153</v>
+        <v>0.5974062768108837</v>
       </c>
     </row>
     <row r="6">
@@ -714,40 +714,40 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1539726483147757</v>
+        <v>0.126176094414458</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05219988618364381</v>
+        <v>0.04791327940912467</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>59.99260928344965</v>
+        <v>39.14583275092971</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006413601258043545</v>
+        <v>0.007518124415006624</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4023144864005901</v>
+        <v>0.3856165154331307</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3931140170889311</v>
+        <v>0.3945288114201675</v>
       </c>
       <c r="K6" t="n">
-        <v>2.153894214091423</v>
+        <v>2.303926135717681</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2534982534432125</v>
+        <v>-0.0004710425412296048</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3782667062170901</v>
+        <v>-0.1577504495608363</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3723630141147607</v>
+        <v>0.176265709282811</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6831018026581483</v>
+        <v>1.081440011169387</v>
       </c>
     </row>
     <row r="7">
@@ -763,40 +763,40 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1485806114128822</v>
+        <v>0.1485672379129818</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05245648712334585</v>
+        <v>0.05009319832789971</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>26.31670551137697</v>
+        <v>26.7497989726661</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007281559057604298</v>
+        <v>0.005262525188478381</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4008533778421772</v>
+        <v>0.3970853870922503</v>
       </c>
       <c r="J7" t="n">
-        <v>0.421242793993894</v>
+        <v>0.413953405098165</v>
       </c>
       <c r="K7" t="n">
-        <v>2.426871659489694</v>
+        <v>2.443875547753798</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2513600927753623</v>
+        <v>0.2399232928015362</v>
       </c>
       <c r="M7" t="n">
-        <v>0.385322480702235</v>
+        <v>0.3869036695220629</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2380991796724366</v>
+        <v>0.2548940119901126</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.02238401476897605</v>
+        <v>-0.04016494703747209</v>
       </c>
     </row>
     <row r="8">
@@ -812,40 +812,40 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09870526653052931</v>
+        <v>0.09651712075023249</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04273066177694543</v>
+        <v>0.04357141008926278</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>35.65723462265144</v>
+        <v>18.05667712743425</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002918597112675284</v>
+        <v>0.005511646149815067</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3882706649423203</v>
+        <v>0.379460764348199</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5312832446391645</v>
+        <v>0.5293412824551285</v>
       </c>
       <c r="K8" t="n">
-        <v>1.999286954720624</v>
+        <v>1.961897172743173</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.01991117448202358</v>
+        <v>0.0452937126901163</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0373186709377998</v>
+        <v>0.03307503318409424</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1343341731495304</v>
+        <v>0.1596425294303053</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1603946198391386</v>
+        <v>0.1207200654339963</v>
       </c>
     </row>
   </sheetData>
